--- a/public/StructureDefinition-PhrBundle.xlsx
+++ b/public/StructureDefinition-PhrBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot</t>
+    <t>1.0.0-ballot2</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T16:03:27-05:00</t>
+    <t>2026-04-16T16:46:43-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1803,17 +1803,17 @@
   <dimension ref="A1:AN241"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="63.875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.640625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="26.6953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="20.6328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.09765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.46875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.02734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="17.796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="18.921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="16.32421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1822,26 +1822,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="162.69140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.01171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="37.59765625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="33.6640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="140.34375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.140625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="32.43359375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.0390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.75" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="22.6796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="41.6640625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="22.2109375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="19.5625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="35.9375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="28.5078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7290,7 +7290,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>266</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>300</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
         <v>334</v>
       </c>
@@ -18162,7 +18162,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
         <v>367</v>
       </c>
@@ -21786,7 +21786,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="177" hidden="true">
+    <row r="177">
       <c r="A177" t="s" s="2">
         <v>401</v>
       </c>
@@ -25410,7 +25410,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="209" hidden="true">
+    <row r="209">
       <c r="A209" t="s" s="2">
         <v>435</v>
       </c>
@@ -29152,12 +29152,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN241">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/public/StructureDefinition-PhrBundle.xlsx
+++ b/public/StructureDefinition-PhrBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T16:46:43-05:00</t>
+    <t>2026-04-23T16:43:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-PhrBundle.xlsx
+++ b/public/StructureDefinition-PhrBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T16:43:45-05:00</t>
+    <t>2026-04-23T17:08:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-PhrBundle.xlsx
+++ b/public/StructureDefinition-PhrBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T17:08:04-05:00</t>
+    <t>2026-06-11T13:06:45-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-PhrBundle.xlsx
+++ b/public/StructureDefinition-PhrBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T13:06:45-06:00</t>
+    <t>2026-06-11T16:28:41-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
